--- a/uranai/data/町名グループ.xlsx
+++ b/uranai/data/町名グループ.xlsx
@@ -2687,3124 +2687,2960 @@
   </sheetPr>
   <dimension ref="A1:E164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>配信スケジュール(週×順)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>土曜の占いで使う町を1行ずつ並べた表。配信予定日を埋めて運用してください。</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>週</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>順番</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>町名</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>ヨミカタ</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>南大通</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>ミナミオオドオリ</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>本野町</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>ホンノチョウ</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>豊が丘町</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>ユタカガオカチョウ</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>国府町</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>コウチョウ</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>新宿町</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>シンジュクチョウ</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>桜ケ丘町</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>サクラガオカチョウ</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>土筒町</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>ドドウチョウ</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="A12" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>谷川町</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>ヤガワチョウ</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>西口町</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>ニシグチチョウ</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="A14" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>新豊町</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>シンユタカマチ</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>四ツ谷町</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>ヨツヤチョウ</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="A16" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>大木新町通</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>オオギシンマチドオリ</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>松原町</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>マツバラチョウ</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="A18" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>平尾町</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>ヒラオチョウ</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>東名町</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>トウメイチョウ</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" t="n">
         <v>6</v>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>赤坂台</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>アカサカダイ</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" t="n">
         <v>7</v>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>馬場町</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>ババチョウ</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>光陽町</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>コウヨウチョウ</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" t="n">
         <v>9</v>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>諏訪</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>スワ</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>金屋本町</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>カナヤホンマチ</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B25" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>東上町</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>トウジョウチョウ</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B26" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>赤代町</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>アカシロチョウ</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B27" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>本野ケ原</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>ホンノガハラ</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n">
+      <c r="A28" t="n">
         <v>3</v>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B28" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>三蔵子町</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>サンゾウゴチョウ</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>高見町</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>タカミチョウ</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="A30" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="10" t="n">
+      <c r="B30" t="n">
         <v>6</v>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>柑子町</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>コウジチョウ</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="10" t="n">
+      <c r="B31" t="n">
         <v>7</v>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>豊栄町</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>ホウエイチョウ</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="A32" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="10" t="n">
+      <c r="B32" t="n">
         <v>8</v>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>美幸町</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>ミユキチョウ</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n">
+      <c r="A33" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="10" t="n">
+      <c r="B33" t="n">
         <v>9</v>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>白雲町</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>シラクモチョウ</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="10" t="n">
+      <c r="B34" t="n">
         <v>10</v>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>橋尾町</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>ハシオチョウ</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n">
+      <c r="A35" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="10" t="n">
+      <c r="B35" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>新青馬町</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>シンアオウマチョウ</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n">
+      <c r="A36" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="10" t="n">
+      <c r="B36" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>明野町</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>アケノチョウ</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n">
+      <c r="A37" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="10" t="n">
+      <c r="B37" t="n">
         <v>3</v>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>豊川西町</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>トヨカワニシマチ</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n">
+      <c r="A38" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="10" t="n">
+      <c r="B38" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>佐土町</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>サドチョウ</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n">
+      <c r="A39" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="10" t="n">
+      <c r="B39" t="n">
         <v>5</v>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>上長山町</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>カミナガヤマチョウ</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n">
+      <c r="A40" t="n">
         <v>4</v>
       </c>
-      <c r="B40" s="10" t="n">
+      <c r="B40" t="n">
         <v>6</v>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>豊川仲町</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>トヨカワナカマチ</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="n">
+      <c r="A41" t="n">
         <v>4</v>
       </c>
-      <c r="B41" s="10" t="n">
+      <c r="B41" t="n">
         <v>7</v>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>牛久保駅通</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>ウシクボエキドオリ</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n">
+      <c r="A42" t="n">
         <v>4</v>
       </c>
-      <c r="B42" s="10" t="n">
+      <c r="B42" t="n">
         <v>8</v>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>美和通</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>ミワドオリ</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n">
+      <c r="A43" t="n">
         <v>4</v>
       </c>
-      <c r="B43" s="10" t="n">
+      <c r="B43" t="n">
         <v>9</v>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>白鳥町</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>シロトリチョウ</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n">
+      <c r="A44" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="10" t="n">
+      <c r="B44" t="n">
         <v>10</v>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>緑町</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>ミドリマチ</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n">
+      <c r="A45" t="n">
         <v>5</v>
       </c>
-      <c r="B45" s="10" t="n">
+      <c r="B45" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>穂ノ原</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>ホノハラ</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="n">
+      <c r="A46" t="n">
         <v>5</v>
       </c>
-      <c r="B46" s="10" t="n">
+      <c r="B46" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>豊川栄町</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>トヨカワサカエマチ</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="n">
+      <c r="A47" t="n">
         <v>5</v>
       </c>
-      <c r="B47" s="10" t="n">
+      <c r="B47" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>中央通</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>チュウオウドオリ</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="n">
+      <c r="A48" t="n">
         <v>5</v>
       </c>
-      <c r="B48" s="10" t="n">
+      <c r="B48" t="n">
         <v>4</v>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>西桜木町</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>ニシサクラギチョウ</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="n">
+      <c r="A49" t="n">
         <v>5</v>
       </c>
-      <c r="B49" s="10" t="n">
+      <c r="B49" t="n">
         <v>5</v>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>牧野町</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>マキノチョウ</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n">
+      <c r="A50" t="n">
         <v>5</v>
       </c>
-      <c r="B50" s="10" t="n">
+      <c r="B50" t="n">
         <v>6</v>
       </c>
-      <c r="C50" s="11" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>御津町</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>ミトチョウ</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="n">
+      <c r="A51" t="n">
         <v>5</v>
       </c>
-      <c r="B51" s="10" t="n">
+      <c r="B51" t="n">
         <v>7</v>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>豊川元町</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>トヨカワモトマチ</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="n">
+      <c r="A52" t="n">
         <v>5</v>
       </c>
-      <c r="B52" s="10" t="n">
+      <c r="B52" t="n">
         <v>8</v>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>駅前通</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>エキマエドオリ</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="n">
+      <c r="A53" t="n">
         <v>5</v>
       </c>
-      <c r="B53" s="10" t="n">
+      <c r="B53" t="n">
         <v>9</v>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>樽井町</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>タルイチョウ</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="n">
+      <c r="A54" t="n">
         <v>5</v>
       </c>
-      <c r="B54" s="10" t="n">
+      <c r="B54" t="n">
         <v>10</v>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>新桜町通</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>シンサクラマチドオリ</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="n">
+      <c r="A55" t="n">
         <v>6</v>
       </c>
-      <c r="B55" s="10" t="n">
+      <c r="B55" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>佐奈川町</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>サナガワチョウ</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="n">
+      <c r="A56" t="n">
         <v>6</v>
       </c>
-      <c r="B56" s="10" t="n">
+      <c r="B56" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="11" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>金沢町</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>カナザワチョウ</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n">
+      <c r="A57" t="n">
         <v>6</v>
       </c>
-      <c r="B57" s="10" t="n">
+      <c r="B57" t="n">
         <v>3</v>
       </c>
-      <c r="C57" s="11" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>瀬木町</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>セギチョウ</t>
         </is>
       </c>
-      <c r="E57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n">
+      <c r="A58" t="n">
         <v>6</v>
       </c>
-      <c r="B58" s="10" t="n">
+      <c r="B58" t="n">
         <v>4</v>
       </c>
-      <c r="C58" s="11" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>蔵子</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>ゾウシ</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="n">
+      <c r="A59" t="n">
         <v>6</v>
       </c>
-      <c r="B59" s="10" t="n">
+      <c r="B59" t="n">
         <v>5</v>
       </c>
-      <c r="C59" s="11" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>宿町</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>シュクチョウ</t>
         </is>
       </c>
-      <c r="E59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="n">
+      <c r="A60" t="n">
         <v>6</v>
       </c>
-      <c r="B60" s="10" t="n">
+      <c r="B60" t="n">
         <v>6</v>
       </c>
-      <c r="C60" s="11" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>中野川町</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>ナカノガワチョウ</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="n">
+      <c r="A61" t="n">
         <v>6</v>
       </c>
-      <c r="B61" s="10" t="n">
+      <c r="B61" t="n">
         <v>7</v>
       </c>
-      <c r="C61" s="11" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>天神町</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>テンジンチョウ</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="n">
+      <c r="A62" t="n">
         <v>6</v>
       </c>
-      <c r="B62" s="10" t="n">
+      <c r="B62" t="n">
         <v>8</v>
       </c>
-      <c r="C62" s="11" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>美園</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>ミソノ</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="n">
+      <c r="A63" t="n">
         <v>6</v>
       </c>
-      <c r="B63" s="10" t="n">
+      <c r="B63" t="n">
         <v>9</v>
       </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>久保町</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>クボチョウ</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="n">
+      <c r="A64" t="n">
         <v>6</v>
       </c>
-      <c r="B64" s="10" t="n">
+      <c r="B64" t="n">
         <v>10</v>
       </c>
-      <c r="C64" s="11" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>東光町</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>トウコウチョウ</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="n">
+      <c r="A65" t="n">
         <v>7</v>
       </c>
-      <c r="B65" s="10" t="n">
+      <c r="B65" t="n">
         <v>1</v>
       </c>
-      <c r="C65" s="11" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>二葉町</t>
         </is>
       </c>
-      <c r="D65" s="11" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>フタバチョウ</t>
         </is>
       </c>
-      <c r="E65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="n">
+      <c r="A66" t="n">
         <v>7</v>
       </c>
-      <c r="B66" s="10" t="n">
+      <c r="B66" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>新栄町</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>シンサカエマチ</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="n">
+      <c r="A67" t="n">
         <v>7</v>
       </c>
-      <c r="B67" s="10" t="n">
+      <c r="B67" t="n">
         <v>3</v>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>江島町</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>エジマチョウ</t>
         </is>
       </c>
-      <c r="E67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="n">
+      <c r="A68" t="n">
         <v>7</v>
       </c>
-      <c r="B68" s="10" t="n">
+      <c r="B68" t="n">
         <v>4</v>
       </c>
-      <c r="C68" s="11" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>桜町</t>
         </is>
       </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>サクラマチ</t>
         </is>
       </c>
-      <c r="E68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="n">
+      <c r="A69" t="n">
         <v>7</v>
       </c>
-      <c r="B69" s="10" t="n">
+      <c r="B69" t="n">
         <v>5</v>
       </c>
-      <c r="C69" s="11" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>松風町</t>
         </is>
       </c>
-      <c r="D69" s="11" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>マツカゼチョウ</t>
         </is>
       </c>
-      <c r="E69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="n">
+      <c r="A70" t="n">
         <v>7</v>
       </c>
-      <c r="B70" s="10" t="n">
+      <c r="B70" t="n">
         <v>6</v>
       </c>
-      <c r="C70" s="11" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>曙町</t>
         </is>
       </c>
-      <c r="D70" s="11" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>アケボノチョウ</t>
         </is>
       </c>
-      <c r="E70" s="11" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="n">
+      <c r="A71" t="n">
         <v>7</v>
       </c>
-      <c r="B71" s="10" t="n">
+      <c r="B71" t="n">
         <v>7</v>
       </c>
-      <c r="C71" s="11" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>古宿町</t>
         </is>
       </c>
-      <c r="D71" s="11" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>フルジュクチョウ</t>
         </is>
       </c>
-      <c r="E71" s="11" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="n">
+      <c r="A72" t="n">
         <v>7</v>
       </c>
-      <c r="B72" s="10" t="n">
+      <c r="B72" t="n">
         <v>8</v>
       </c>
-      <c r="C72" s="11" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>向河原町</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>ムコウガワラチョウ</t>
         </is>
       </c>
-      <c r="E72" s="11" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="10" t="n">
+      <c r="A73" t="n">
         <v>7</v>
       </c>
-      <c r="B73" s="10" t="n">
+      <c r="B73" t="n">
         <v>9</v>
       </c>
-      <c r="C73" s="11" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>光明町</t>
         </is>
       </c>
-      <c r="D73" s="11" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>コウメイチョウ</t>
         </is>
       </c>
-      <c r="E73" s="11" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="n">
+      <c r="A74" t="n">
         <v>7</v>
       </c>
-      <c r="B74" s="10" t="n">
+      <c r="B74" t="n">
         <v>10</v>
       </c>
-      <c r="C74" s="11" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>若宮町</t>
         </is>
       </c>
-      <c r="D74" s="11" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>ワカミヤチョウ</t>
         </is>
       </c>
-      <c r="E74" s="11" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="10" t="n">
+      <c r="A75" t="n">
         <v>8</v>
       </c>
-      <c r="B75" s="10" t="n">
+      <c r="B75" t="n">
         <v>1</v>
       </c>
-      <c r="C75" s="11" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>長沢町</t>
         </is>
       </c>
-      <c r="D75" s="11" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>ナガサワチョウ</t>
         </is>
       </c>
-      <c r="E75" s="11" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="n">
+      <c r="A76" t="n">
         <v>8</v>
       </c>
-      <c r="B76" s="10" t="n">
+      <c r="B76" t="n">
         <v>2</v>
       </c>
-      <c r="C76" s="11" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>東新町</t>
         </is>
       </c>
-      <c r="D76" s="11" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>トウシンチョウ</t>
         </is>
       </c>
-      <c r="E76" s="11" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="n">
+      <c r="A77" t="n">
         <v>8</v>
       </c>
-      <c r="B77" s="10" t="n">
+      <c r="B77" t="n">
         <v>3</v>
       </c>
-      <c r="C77" s="11" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>山道町</t>
         </is>
       </c>
-      <c r="D77" s="11" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>ヤマミチチョウ</t>
         </is>
       </c>
-      <c r="E77" s="11" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="n">
+      <c r="A78" t="n">
         <v>8</v>
       </c>
-      <c r="B78" s="10" t="n">
+      <c r="B78" t="n">
         <v>4</v>
       </c>
-      <c r="C78" s="11" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>中条町</t>
         </is>
       </c>
-      <c r="D78" s="11" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>チュウジョウチョウ</t>
         </is>
       </c>
-      <c r="E78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="n">
+      <c r="A79" t="n">
         <v>8</v>
       </c>
-      <c r="B79" s="10" t="n">
+      <c r="B79" t="n">
         <v>5</v>
       </c>
-      <c r="C79" s="11" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>金屋元町</t>
         </is>
       </c>
-      <c r="D79" s="11" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>カナヤモトマチ</t>
         </is>
       </c>
-      <c r="E79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="n">
+      <c r="A80" t="n">
         <v>8</v>
       </c>
-      <c r="B80" s="10" t="n">
+      <c r="B80" t="n">
         <v>6</v>
       </c>
-      <c r="C80" s="11" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>東曙町</t>
         </is>
       </c>
-      <c r="D80" s="11" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>ヒガシアケボノチョウ</t>
         </is>
       </c>
-      <c r="E80" s="11" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="n">
+      <c r="A81" t="n">
         <v>8</v>
       </c>
-      <c r="B81" s="10" t="n">
+      <c r="B81" t="n">
         <v>7</v>
       </c>
-      <c r="C81" s="11" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>大橋町</t>
         </is>
       </c>
-      <c r="D81" s="11" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>オオハシチョウ</t>
         </is>
       </c>
-      <c r="E81" s="11" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="n">
+      <c r="A82" t="n">
         <v>8</v>
       </c>
-      <c r="B82" s="10" t="n">
+      <c r="B82" t="n">
         <v>8</v>
       </c>
-      <c r="C82" s="11" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>三上町</t>
         </is>
       </c>
-      <c r="D82" s="11" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>ミカミチョウ</t>
         </is>
       </c>
-      <c r="E82" s="11" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="n">
+      <c r="A83" t="n">
         <v>8</v>
       </c>
-      <c r="B83" s="10" t="n">
+      <c r="B83" t="n">
         <v>9</v>
       </c>
-      <c r="C83" s="11" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>一宮町</t>
         </is>
       </c>
-      <c r="D83" s="11" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>イチノミヤチョウ</t>
         </is>
       </c>
-      <c r="E83" s="11" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="n">
+      <c r="A84" t="n">
         <v>8</v>
       </c>
-      <c r="B84" s="10" t="n">
+      <c r="B84" t="n">
         <v>10</v>
       </c>
-      <c r="C84" s="11" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>北浦町</t>
         </is>
       </c>
-      <c r="D84" s="11" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>キタウラチョウ</t>
         </is>
       </c>
-      <c r="E84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="n">
+      <c r="A85" t="n">
         <v>9</v>
       </c>
-      <c r="B85" s="10" t="n">
+      <c r="B85" t="n">
         <v>1</v>
       </c>
-      <c r="C85" s="11" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>弥生町</t>
         </is>
       </c>
-      <c r="D85" s="11" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>ヤヨイチョウ</t>
         </is>
       </c>
-      <c r="E85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="n">
+      <c r="A86" t="n">
         <v>9</v>
       </c>
-      <c r="B86" s="10" t="n">
+      <c r="B86" t="n">
         <v>2</v>
       </c>
-      <c r="C86" s="11" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>東桜木町</t>
         </is>
       </c>
-      <c r="D86" s="11" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>ヒガシサクラギチョウ</t>
         </is>
       </c>
-      <c r="E86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="n">
+      <c r="A87" t="n">
         <v>9</v>
       </c>
-      <c r="B87" s="10" t="n">
+      <c r="B87" t="n">
         <v>3</v>
       </c>
-      <c r="C87" s="11" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>幸町</t>
         </is>
       </c>
-      <c r="D87" s="11" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>サイワイチョウ</t>
         </is>
       </c>
-      <c r="E87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="n">
+      <c r="A88" t="n">
         <v>9</v>
       </c>
-      <c r="B88" s="10" t="n">
+      <c r="B88" t="n">
         <v>4</v>
       </c>
-      <c r="C88" s="11" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>大崎町</t>
         </is>
       </c>
-      <c r="D88" s="11" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>オオサキチョウ</t>
         </is>
       </c>
-      <c r="E88" s="11" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="n">
+      <c r="A89" t="n">
         <v>9</v>
       </c>
-      <c r="B89" s="10" t="n">
+      <c r="B89" t="n">
         <v>5</v>
       </c>
-      <c r="C89" s="11" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>長草町</t>
         </is>
       </c>
-      <c r="D89" s="11" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>ナガクサチョウ</t>
         </is>
       </c>
-      <c r="E89" s="11" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="n">
+      <c r="A90" t="n">
         <v>9</v>
       </c>
-      <c r="B90" s="10" t="n">
+      <c r="B90" t="n">
         <v>6</v>
       </c>
-      <c r="C90" s="11" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>千歳通</t>
         </is>
       </c>
-      <c r="D90" s="11" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>チトセドオリ</t>
         </is>
       </c>
-      <c r="E90" s="11" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="10" t="n">
+      <c r="A91" t="n">
         <v>9</v>
       </c>
-      <c r="B91" s="10" t="n">
+      <c r="B91" t="n">
         <v>7</v>
       </c>
-      <c r="C91" s="11" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>西豊町</t>
         </is>
       </c>
-      <c r="D91" s="11" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>ニシユタカマチ</t>
         </is>
       </c>
-      <c r="E91" s="11" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="n">
+      <c r="A92" t="n">
         <v>9</v>
       </c>
-      <c r="B92" s="10" t="n">
+      <c r="B92" t="n">
         <v>8</v>
       </c>
-      <c r="C92" s="11" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>八幡町</t>
         </is>
       </c>
-      <c r="D92" s="11" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>ヤワタチョウ</t>
         </is>
       </c>
-      <c r="E92" s="11" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="n">
+      <c r="A93" t="n">
         <v>9</v>
       </c>
-      <c r="B93" s="10" t="n">
+      <c r="B93" t="n">
         <v>9</v>
       </c>
-      <c r="C93" s="11" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>西塚町</t>
         </is>
       </c>
-      <c r="D93" s="11" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>ニシヅカチョウ</t>
         </is>
       </c>
-      <c r="E93" s="11" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="n">
+      <c r="A94" t="n">
         <v>9</v>
       </c>
-      <c r="B94" s="10" t="n">
+      <c r="B94" t="n">
         <v>10</v>
       </c>
-      <c r="C94" s="11" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>東豊町</t>
         </is>
       </c>
-      <c r="D94" s="11" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>ヒガシユタカマチ</t>
         </is>
       </c>
-      <c r="E94" s="11" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="n">
+      <c r="A95" t="n">
         <v>10</v>
       </c>
-      <c r="B95" s="10" t="n">
+      <c r="B95" t="n">
         <v>1</v>
       </c>
-      <c r="C95" s="11" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>野口町</t>
         </is>
       </c>
-      <c r="D95" s="11" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>ノグチチョウ</t>
         </is>
       </c>
-      <c r="E95" s="11" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="n">
+      <c r="A96" t="n">
         <v>10</v>
       </c>
-      <c r="B96" s="10" t="n">
+      <c r="B96" t="n">
         <v>2</v>
       </c>
-      <c r="C96" s="11" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>西島町</t>
         </is>
       </c>
-      <c r="D96" s="11" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>ニシジマチョウ</t>
         </is>
       </c>
-      <c r="E96" s="11" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="10" t="n">
+      <c r="A97" t="n">
         <v>10</v>
       </c>
-      <c r="B97" s="10" t="n">
+      <c r="B97" t="n">
         <v>3</v>
       </c>
-      <c r="C97" s="11" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>萩山町</t>
         </is>
       </c>
-      <c r="D97" s="11" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>ハギヤマチョウ</t>
         </is>
       </c>
-      <c r="E97" s="11" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="n">
+      <c r="A98" t="n">
         <v>10</v>
       </c>
-      <c r="B98" s="10" t="n">
+      <c r="B98" t="n">
         <v>4</v>
       </c>
-      <c r="C98" s="11" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>金屋橋町</t>
         </is>
       </c>
-      <c r="D98" s="11" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>カナヤバシチョウ</t>
         </is>
       </c>
-      <c r="E98" s="11" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="10" t="n">
+      <c r="A99" t="n">
         <v>10</v>
       </c>
-      <c r="B99" s="10" t="n">
+      <c r="B99" t="n">
         <v>5</v>
       </c>
-      <c r="C99" s="11" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>中部町</t>
         </is>
       </c>
-      <c r="D99" s="11" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>チュウブチョウ</t>
         </is>
       </c>
-      <c r="E99" s="11" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="n">
+      <c r="A100" t="n">
         <v>10</v>
       </c>
-      <c r="B100" s="10" t="n">
+      <c r="B100" t="n">
         <v>6</v>
       </c>
-      <c r="C100" s="11" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>萩町</t>
         </is>
       </c>
-      <c r="D100" s="11" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>ハギチョウ</t>
         </is>
       </c>
-      <c r="E100" s="11" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="n">
+      <c r="A101" t="n">
         <v>10</v>
       </c>
-      <c r="B101" s="10" t="n">
+      <c r="B101" t="n">
         <v>7</v>
       </c>
-      <c r="C101" s="11" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>森</t>
         </is>
       </c>
-      <c r="D101" s="11" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>モリ</t>
         </is>
       </c>
-      <c r="E101" s="11" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="n">
+      <c r="A102" t="n">
         <v>10</v>
       </c>
-      <c r="B102" s="10" t="n">
+      <c r="B102" t="n">
         <v>8</v>
       </c>
-      <c r="C102" s="11" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>塔ノ木町</t>
         </is>
       </c>
-      <c r="D102" s="11" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>トウノギチョウ</t>
         </is>
       </c>
-      <c r="E102" s="11" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="n">
+      <c r="A103" t="n">
         <v>10</v>
       </c>
-      <c r="B103" s="10" t="n">
+      <c r="B103" t="n">
         <v>9</v>
       </c>
-      <c r="C103" s="11" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>開運通</t>
         </is>
       </c>
-      <c r="D103" s="11" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>カイウンドオリ</t>
         </is>
       </c>
-      <c r="E103" s="11" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="n">
+      <c r="A104" t="n">
         <v>10</v>
       </c>
-      <c r="B104" s="10" t="n">
+      <c r="B104" t="n">
         <v>10</v>
       </c>
-      <c r="C104" s="11" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>諏訪西町</t>
         </is>
       </c>
-      <c r="D104" s="11" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>スワニシマチ</t>
         </is>
       </c>
-      <c r="E104" s="11" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="10" t="n">
+      <c r="A105" t="n">
         <v>11</v>
       </c>
-      <c r="B105" s="10" t="n">
+      <c r="B105" t="n">
         <v>1</v>
       </c>
-      <c r="C105" s="11" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>御油町</t>
         </is>
       </c>
-      <c r="D105" s="11" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>ゴユチョウ</t>
         </is>
       </c>
-      <c r="E105" s="11" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="n">
+      <c r="A106" t="n">
         <v>11</v>
       </c>
-      <c r="B106" s="10" t="n">
+      <c r="B106" t="n">
         <v>2</v>
       </c>
-      <c r="C106" s="11" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>代田町</t>
         </is>
       </c>
-      <c r="D106" s="11" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>ダイダチョウ</t>
         </is>
       </c>
-      <c r="E106" s="11" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="10" t="n">
+      <c r="A107" t="n">
         <v>11</v>
       </c>
-      <c r="B107" s="10" t="n">
+      <c r="B107" t="n">
         <v>3</v>
       </c>
-      <c r="C107" s="11" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>千両町</t>
         </is>
       </c>
-      <c r="D107" s="11" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>チギリチョウ</t>
         </is>
       </c>
-      <c r="E107" s="11" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="n">
+      <c r="A108" t="n">
         <v>11</v>
       </c>
-      <c r="B108" s="10" t="n">
+      <c r="B108" t="n">
         <v>4</v>
       </c>
-      <c r="C108" s="11" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>光輝町</t>
         </is>
       </c>
-      <c r="D108" s="11" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>コウキチョウ</t>
         </is>
       </c>
-      <c r="E108" s="11" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="10" t="n">
+      <c r="A109" t="n">
         <v>11</v>
       </c>
-      <c r="B109" s="10" t="n">
+      <c r="B109" t="n">
         <v>5</v>
       </c>
-      <c r="C109" s="11" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>六角町</t>
         </is>
       </c>
-      <c r="D109" s="11" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>ロッカクチョウ</t>
         </is>
       </c>
-      <c r="E109" s="11" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="n">
+      <c r="A110" t="n">
         <v>11</v>
       </c>
-      <c r="B110" s="10" t="n">
+      <c r="B110" t="n">
         <v>6</v>
       </c>
-      <c r="C110" s="11" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>伊奈町</t>
         </is>
       </c>
-      <c r="D110" s="11" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>イナチョウ</t>
         </is>
       </c>
-      <c r="E110" s="11" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="10" t="n">
+      <c r="A111" t="n">
         <v>11</v>
       </c>
-      <c r="B111" s="10" t="n">
+      <c r="B111" t="n">
         <v>7</v>
       </c>
-      <c r="C111" s="11" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>平井町</t>
         </is>
       </c>
-      <c r="D111" s="11" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>ヒライチョウ</t>
         </is>
       </c>
-      <c r="E111" s="11" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="10" t="n">
+      <c r="A112" t="n">
         <v>11</v>
       </c>
-      <c r="B112" s="10" t="n">
+      <c r="B112" t="n">
         <v>8</v>
       </c>
-      <c r="C112" s="11" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>牛久保町</t>
         </is>
       </c>
-      <c r="D112" s="11" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>ウシクボチョウ</t>
         </is>
       </c>
-      <c r="E112" s="11" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="10" t="n">
+      <c r="A113" t="n">
         <v>11</v>
       </c>
-      <c r="B113" s="10" t="n">
+      <c r="B113" t="n">
         <v>9</v>
       </c>
-      <c r="C113" s="11" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>新道町</t>
         </is>
       </c>
-      <c r="D113" s="11" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>シンミチチョウ</t>
         </is>
       </c>
-      <c r="E113" s="11" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="10" t="n">
+      <c r="A114" t="n">
         <v>11</v>
       </c>
-      <c r="B114" s="10" t="n">
+      <c r="B114" t="n">
         <v>10</v>
       </c>
-      <c r="C114" s="11" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>下長山町</t>
         </is>
       </c>
-      <c r="D114" s="11" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>シモナガヤマチョウ</t>
         </is>
       </c>
-      <c r="E114" s="11" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="10" t="n">
+      <c r="A115" t="n">
         <v>12</v>
       </c>
-      <c r="B115" s="10" t="n">
+      <c r="B115" t="n">
         <v>1</v>
       </c>
-      <c r="C115" s="11" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>豊川町</t>
         </is>
       </c>
-      <c r="D115" s="11" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>トヨカワチョウ</t>
         </is>
       </c>
-      <c r="E115" s="11" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="10" t="n">
+      <c r="A116" t="n">
         <v>12</v>
       </c>
-      <c r="B116" s="10" t="n">
+      <c r="B116" t="n">
         <v>2</v>
       </c>
-      <c r="C116" s="11" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>旭町</t>
         </is>
       </c>
-      <c r="D116" s="11" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>アサヒマチ</t>
         </is>
       </c>
-      <c r="E116" s="11" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="10" t="n">
+      <c r="A117" t="n">
         <v>12</v>
       </c>
-      <c r="B117" s="10" t="n">
+      <c r="B117" t="n">
         <v>3</v>
       </c>
-      <c r="C117" s="11" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>西香ノ木町</t>
         </is>
       </c>
-      <c r="D117" s="11" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>ニシコウノギチョウ</t>
         </is>
       </c>
-      <c r="E117" s="11" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="10" t="n">
+      <c r="A118" t="n">
         <v>12</v>
       </c>
-      <c r="B118" s="10" t="n">
+      <c r="B118" t="n">
         <v>4</v>
       </c>
-      <c r="C118" s="11" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>川花町</t>
         </is>
       </c>
-      <c r="D118" s="11" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>カワハナチョウ</t>
         </is>
       </c>
-      <c r="E118" s="11" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="10" t="n">
+      <c r="A119" t="n">
         <v>12</v>
       </c>
-      <c r="B119" s="10" t="n">
+      <c r="B119" t="n">
         <v>5</v>
       </c>
-      <c r="C119" s="11" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>為当町</t>
         </is>
       </c>
-      <c r="D119" s="11" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>タメトウチョウ</t>
         </is>
       </c>
-      <c r="E119" s="11" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="10" t="n">
+      <c r="A120" t="n">
         <v>12</v>
       </c>
-      <c r="B120" s="10" t="n">
+      <c r="B120" t="n">
         <v>6</v>
       </c>
-      <c r="C120" s="11" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>小桜町</t>
         </is>
       </c>
-      <c r="D120" s="11" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>コザクラチョウ</t>
         </is>
       </c>
-      <c r="E120" s="11" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="10" t="n">
+      <c r="A121" t="n">
         <v>12</v>
       </c>
-      <c r="B121" s="10" t="n">
+      <c r="B121" t="n">
         <v>7</v>
       </c>
-      <c r="C121" s="11" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>南千両</t>
         </is>
       </c>
-      <c r="D121" s="11" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>ミナミチギリ</t>
         </is>
       </c>
-      <c r="E121" s="11" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="10" t="n">
+      <c r="A122" t="n">
         <v>12</v>
       </c>
-      <c r="B122" s="10" t="n">
+      <c r="B122" t="n">
         <v>8</v>
       </c>
-      <c r="C122" s="11" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>寿通</t>
         </is>
       </c>
-      <c r="D122" s="11" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>コトブキドオリ</t>
         </is>
       </c>
-      <c r="E122" s="11" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="10" t="n">
+      <c r="A123" t="n">
         <v>12</v>
       </c>
-      <c r="B123" s="10" t="n">
+      <c r="B123" t="n">
         <v>9</v>
       </c>
-      <c r="C123" s="11" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>院之子町</t>
         </is>
       </c>
-      <c r="D123" s="11" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>インノコチョウ</t>
         </is>
       </c>
-      <c r="E123" s="11" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="n">
+      <c r="A124" t="n">
         <v>12</v>
       </c>
-      <c r="B124" s="10" t="n">
+      <c r="B124" t="n">
         <v>10</v>
       </c>
-      <c r="C124" s="11" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>堺町</t>
         </is>
       </c>
-      <c r="D124" s="11" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>サカイマチ</t>
         </is>
       </c>
-      <c r="E124" s="11" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="10" t="n">
+      <c r="A125" t="n">
         <v>13</v>
       </c>
-      <c r="B125" s="10" t="n">
+      <c r="B125" t="n">
         <v>1</v>
       </c>
-      <c r="C125" s="11" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>稲荷通</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>イナリドオリ</t>
         </is>
       </c>
-      <c r="E125" s="11" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="n">
+      <c r="A126" t="n">
         <v>13</v>
       </c>
-      <c r="B126" s="10" t="n">
+      <c r="B126" t="n">
         <v>2</v>
       </c>
-      <c r="C126" s="11" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>上野</t>
         </is>
       </c>
-      <c r="D126" s="11" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>ウエノ</t>
         </is>
       </c>
-      <c r="E126" s="11" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="10" t="n">
+      <c r="A127" t="n">
         <v>13</v>
       </c>
-      <c r="B127" s="10" t="n">
+      <c r="B127" t="n">
         <v>3</v>
       </c>
-      <c r="C127" s="11" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>小坂井町</t>
         </is>
       </c>
-      <c r="D127" s="11" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>コザカイチョウ</t>
         </is>
       </c>
-      <c r="E127" s="11" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="10" t="n">
+      <c r="A128" t="n">
         <v>13</v>
       </c>
-      <c r="B128" s="10" t="n">
+      <c r="B128" t="n">
         <v>4</v>
       </c>
-      <c r="C128" s="11" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>豊津町</t>
         </is>
       </c>
-      <c r="D128" s="11" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>トヨツチョウ</t>
         </is>
       </c>
-      <c r="E128" s="11" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="10" t="n">
+      <c r="A129" t="n">
         <v>13</v>
       </c>
-      <c r="B129" s="10" t="n">
+      <c r="B129" t="n">
         <v>5</v>
       </c>
-      <c r="C129" s="11" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>二見町</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>フタミチョウ</t>
         </is>
       </c>
-      <c r="E129" s="11" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="10" t="n">
+      <c r="A130" t="n">
         <v>13</v>
       </c>
-      <c r="B130" s="10" t="n">
+      <c r="B130" t="n">
         <v>6</v>
       </c>
-      <c r="C130" s="11" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>金屋町</t>
         </is>
       </c>
-      <c r="D130" s="11" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>カナヤチョウ</t>
         </is>
       </c>
-      <c r="E130" s="11" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="10" t="n">
+      <c r="A131" t="n">
         <v>13</v>
       </c>
-      <c r="B131" s="10" t="n">
+      <c r="B131" t="n">
         <v>7</v>
       </c>
-      <c r="C131" s="11" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>大木町</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>オオギチョウ</t>
         </is>
       </c>
-      <c r="E131" s="11" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="10" t="n">
+      <c r="A132" t="n">
         <v>13</v>
       </c>
-      <c r="B132" s="10" t="n">
+      <c r="B132" t="n">
         <v>8</v>
       </c>
-      <c r="C132" s="11" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>松久町</t>
         </is>
       </c>
-      <c r="D132" s="11" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>マツヒサチョウ</t>
         </is>
       </c>
-      <c r="E132" s="11" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="10" t="n">
+      <c r="A133" t="n">
         <v>13</v>
       </c>
-      <c r="B133" s="10" t="n">
+      <c r="B133" t="n">
         <v>9</v>
       </c>
-      <c r="C133" s="11" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>当古町</t>
         </is>
       </c>
-      <c r="D133" s="11" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>トウゴチョウ</t>
         </is>
       </c>
-      <c r="E133" s="11" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="10" t="n">
+      <c r="A134" t="n">
         <v>13</v>
       </c>
-      <c r="B134" s="10" t="n">
+      <c r="B134" t="n">
         <v>10</v>
       </c>
-      <c r="C134" s="11" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>門前町</t>
         </is>
       </c>
-      <c r="D134" s="11" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>モンゼンチョウ</t>
         </is>
       </c>
-      <c r="E134" s="11" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="10" t="n">
+      <c r="A135" t="n">
         <v>14</v>
       </c>
-      <c r="B135" s="10" t="n">
+      <c r="B135" t="n">
         <v>1</v>
       </c>
-      <c r="C135" s="11" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>国府南</t>
         </is>
       </c>
-      <c r="D135" s="11" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>コウミナミ</t>
         </is>
       </c>
-      <c r="E135" s="11" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="10" t="n">
+      <c r="A136" t="n">
         <v>14</v>
       </c>
-      <c r="B136" s="10" t="n">
+      <c r="B136" t="n">
         <v>2</v>
       </c>
-      <c r="C136" s="11" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>赤坂町</t>
         </is>
       </c>
-      <c r="D136" s="11" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>アカサカチョウ</t>
         </is>
       </c>
-      <c r="E136" s="11" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="10" t="n">
+      <c r="A137" t="n">
         <v>14</v>
       </c>
-      <c r="B137" s="10" t="n">
+      <c r="B137" t="n">
         <v>3</v>
       </c>
-      <c r="C137" s="11" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>住吉町</t>
         </is>
       </c>
-      <c r="D137" s="11" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>スミヨシチョウ</t>
         </is>
       </c>
-      <c r="E137" s="11" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="10" t="n">
+      <c r="A138" t="n">
         <v>14</v>
       </c>
-      <c r="B138" s="10" t="n">
+      <c r="B138" t="n">
         <v>4</v>
       </c>
-      <c r="C138" s="11" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>花井町</t>
         </is>
       </c>
-      <c r="D138" s="11" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>ハナイチョウ</t>
         </is>
       </c>
-      <c r="E138" s="11" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="10" t="n">
+      <c r="A139" t="n">
         <v>14</v>
       </c>
-      <c r="B139" s="10" t="n">
+      <c r="B139" t="n">
         <v>5</v>
       </c>
-      <c r="C139" s="11" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>篠田町</t>
         </is>
       </c>
-      <c r="D139" s="11" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>シノダチョウ</t>
         </is>
       </c>
-      <c r="E139" s="11" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="10" t="n">
+      <c r="A140" t="n">
         <v>14</v>
       </c>
-      <c r="B140" s="10" t="n">
+      <c r="B140" t="n">
         <v>6</v>
       </c>
-      <c r="C140" s="11" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>西原町</t>
         </is>
       </c>
-      <c r="D140" s="11" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>ニシバラチョウ</t>
         </is>
       </c>
-      <c r="E140" s="11" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="10" t="n">
+      <c r="A141" t="n">
         <v>14</v>
       </c>
-      <c r="B141" s="10" t="n">
+      <c r="B141" t="n">
         <v>7</v>
       </c>
-      <c r="C141" s="11" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>桜木通</t>
         </is>
       </c>
-      <c r="D141" s="11" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>サクラギドオリ</t>
         </is>
       </c>
-      <c r="E141" s="11" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="10" t="n">
+      <c r="A142" t="n">
         <v>14</v>
       </c>
-      <c r="B142" s="10" t="n">
+      <c r="B142" t="n">
         <v>8</v>
       </c>
-      <c r="C142" s="11" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>若鳩町</t>
         </is>
       </c>
-      <c r="D142" s="11" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>ワカバトチョウ</t>
         </is>
       </c>
-      <c r="E142" s="11" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="10" t="n">
+      <c r="A143" t="n">
         <v>14</v>
       </c>
-      <c r="B143" s="10" t="n">
+      <c r="B143" t="n">
         <v>9</v>
       </c>
-      <c r="C143" s="11" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>正岡町</t>
         </is>
       </c>
-      <c r="D143" s="11" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>マサオカチョウ</t>
         </is>
       </c>
-      <c r="E143" s="11" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="10" t="n">
+      <c r="A144" t="n">
         <v>14</v>
       </c>
-      <c r="B144" s="10" t="n">
+      <c r="B144" t="n">
         <v>10</v>
       </c>
-      <c r="C144" s="11" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>下野川町</t>
         </is>
       </c>
-      <c r="D144" s="11" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>シモノガワチョウ</t>
         </is>
       </c>
-      <c r="E144" s="11" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="10" t="n">
+      <c r="A145" t="n">
         <v>15</v>
       </c>
-      <c r="B145" s="10" t="n">
+      <c r="B145" t="n">
         <v>1</v>
       </c>
-      <c r="C145" s="11" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>財賀町</t>
         </is>
       </c>
-      <c r="D145" s="11" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>ザイカチョウ</t>
         </is>
       </c>
-      <c r="E145" s="11" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="10" t="n">
+      <c r="A146" t="n">
         <v>15</v>
       </c>
-      <c r="B146" s="10" t="n">
+      <c r="B146" t="n">
         <v>2</v>
       </c>
-      <c r="C146" s="11" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>小田渕町</t>
         </is>
       </c>
-      <c r="D146" s="11" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>オダブチチョウ</t>
         </is>
       </c>
-      <c r="E146" s="11" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="10" t="n">
+      <c r="A147" t="n">
         <v>15</v>
       </c>
-      <c r="B147" s="10" t="n">
+      <c r="B147" t="n">
         <v>3</v>
       </c>
-      <c r="C147" s="11" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>麻生田町</t>
         </is>
       </c>
-      <c r="D147" s="11" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>アソウダチョウ</t>
         </is>
       </c>
-      <c r="E147" s="11" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="10" t="n">
+      <c r="A148" t="n">
         <v>15</v>
       </c>
-      <c r="B148" s="10" t="n">
+      <c r="B148" t="n">
         <v>4</v>
       </c>
-      <c r="C148" s="11" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>市田町</t>
         </is>
       </c>
-      <c r="D148" s="11" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>イチダチョウ</t>
         </is>
       </c>
-      <c r="E148" s="11" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="10" t="n">
+      <c r="A149" t="n">
         <v>15</v>
       </c>
-      <c r="B149" s="10" t="n">
+      <c r="B149" t="n">
         <v>5</v>
       </c>
-      <c r="C149" s="11" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>西本町</t>
         </is>
       </c>
-      <c r="D149" s="11" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>ニシホンマチ</t>
         </is>
       </c>
-      <c r="E149" s="11" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="10" t="n">
+      <c r="A150" t="n">
         <v>15</v>
       </c>
-      <c r="B150" s="10" t="n">
+      <c r="B150" t="n">
         <v>6</v>
       </c>
-      <c r="C150" s="11" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>大堀町</t>
         </is>
       </c>
-      <c r="D150" s="11" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>オオボリチョウ</t>
         </is>
       </c>
-      <c r="E150" s="11" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="10" t="n">
+      <c r="A151" t="n">
         <v>15</v>
       </c>
-      <c r="B151" s="10" t="n">
+      <c r="B151" t="n">
         <v>7</v>
       </c>
-      <c r="C151" s="11" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>三谷原町</t>
         </is>
       </c>
-      <c r="D151" s="11" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>ミヤハラチョウ</t>
         </is>
       </c>
-      <c r="E151" s="11" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="10" t="n">
+      <c r="A152" t="n">
         <v>15</v>
       </c>
-      <c r="B152" s="10" t="n">
+      <c r="B152" t="n">
         <v>8</v>
       </c>
-      <c r="C152" s="11" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>金塚町</t>
         </is>
       </c>
-      <c r="D152" s="11" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>カナヅカチョウ</t>
         </is>
       </c>
-      <c r="E152" s="11" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="10" t="n">
+      <c r="A153" t="n">
         <v>15</v>
       </c>
-      <c r="B153" s="10" t="n">
+      <c r="B153" t="n">
         <v>9</v>
       </c>
-      <c r="C153" s="11" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>行明町</t>
         </is>
       </c>
-      <c r="D153" s="11" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>ギョウメイチョウ</t>
         </is>
       </c>
-      <c r="E153" s="11" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="10" t="n">
+      <c r="A154" t="n">
         <v>15</v>
       </c>
-      <c r="B154" s="10" t="n">
+      <c r="B154" t="n">
         <v>10</v>
       </c>
-      <c r="C154" s="11" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>篠束町</t>
         </is>
       </c>
-      <c r="D154" s="11" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>シノヅカチョウ</t>
         </is>
       </c>
-      <c r="E154" s="11" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="10" t="n">
+      <c r="A155" t="n">
         <v>16</v>
       </c>
-      <c r="B155" s="10" t="n">
+      <c r="B155" t="n">
         <v>1</v>
       </c>
-      <c r="C155" s="11" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>白鳥</t>
         </is>
       </c>
-      <c r="D155" s="11" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>シロトリ</t>
         </is>
       </c>
-      <c r="E155" s="11" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="10" t="n">
+      <c r="A156" t="n">
         <v>16</v>
       </c>
-      <c r="B156" s="10" t="n">
+      <c r="B156" t="n">
         <v>2</v>
       </c>
-      <c r="C156" s="11" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>末広通</t>
         </is>
       </c>
-      <c r="D156" s="11" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>スエヒロドオリ</t>
         </is>
       </c>
-      <c r="E156" s="11" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="10" t="n">
+      <c r="A157" t="n">
         <v>16</v>
       </c>
-      <c r="B157" s="10" t="n">
+      <c r="B157" t="n">
         <v>3</v>
       </c>
-      <c r="C157" s="11" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>足山田町</t>
         </is>
       </c>
-      <c r="D157" s="11" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>アシヤマダチョウ</t>
         </is>
       </c>
-      <c r="E157" s="11" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="10" t="n">
+      <c r="A158" t="n">
         <v>16</v>
       </c>
-      <c r="B158" s="10" t="n">
+      <c r="B158" t="n">
         <v>4</v>
       </c>
-      <c r="C158" s="11" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>金屋西町</t>
         </is>
       </c>
-      <c r="D158" s="11" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>カナヤニシマチ</t>
         </is>
       </c>
-      <c r="E158" s="11" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="12" t="n">
+      <c r="A159" t="n">
         <v>16</v>
       </c>
-      <c r="B159" s="12" t="n">
+      <c r="B159" t="n">
         <v>5</v>
       </c>
-      <c r="C159" s="13" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>南大通</t>
         </is>
       </c>
-      <c r="D159" s="13" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>ミナミオオドオリ</t>
         </is>
       </c>
-      <c r="E159" s="13" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>※2周目から先取り</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="12" t="n">
+      <c r="A160" t="n">
         <v>16</v>
       </c>
-      <c r="B160" s="12" t="n">
+      <c r="B160" t="n">
         <v>6</v>
       </c>
-      <c r="C160" s="13" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>本野町</t>
         </is>
       </c>
-      <c r="D160" s="13" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>ホンノチョウ</t>
         </is>
       </c>
-      <c r="E160" s="13" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>※2周目から先取り</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="12" t="n">
+      <c r="A161" t="n">
         <v>16</v>
       </c>
-      <c r="B161" s="12" t="n">
+      <c r="B161" t="n">
         <v>7</v>
       </c>
-      <c r="C161" s="13" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>豊が丘町</t>
         </is>
       </c>
-      <c r="D161" s="13" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>ユタカガオカチョウ</t>
         </is>
       </c>
-      <c r="E161" s="13" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>※2周目から先取り</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="12" t="n">
+      <c r="A162" t="n">
         <v>16</v>
       </c>
-      <c r="B162" s="12" t="n">
+      <c r="B162" t="n">
         <v>8</v>
       </c>
-      <c r="C162" s="13" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>国府町</t>
         </is>
       </c>
-      <c r="D162" s="13" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>コウチョウ</t>
         </is>
       </c>
-      <c r="E162" s="13" t="inlineStr">
+      <c r="E162" t="inlineStr">
         <is>
           <t>※2周目から先取り</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="12" t="n">
+      <c r="A163" t="n">
         <v>16</v>
       </c>
-      <c r="B163" s="12" t="n">
+      <c r="B163" t="n">
         <v>9</v>
       </c>
-      <c r="C163" s="13" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>新宿町</t>
         </is>
       </c>
-      <c r="D163" s="13" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>シンジュクチョウ</t>
         </is>
       </c>
-      <c r="E163" s="13" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>※2周目から先取り</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="12" t="n">
+      <c r="A164" t="n">
         <v>16</v>
       </c>
-      <c r="B164" s="12" t="n">
+      <c r="B164" t="n">
         <v>10</v>
       </c>
-      <c r="C164" s="13" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>桜ケ丘町</t>
         </is>
       </c>
-      <c r="D164" s="13" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>サクラガオカチョウ</t>
         </is>
       </c>
-      <c r="E164" s="13" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>※2周目から先取り</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/uranai/data/町名グループ.xlsx
+++ b/uranai/data/町名グループ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用ルール_必読" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="グループ一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配信スケジュール" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全町リスト_五十音順" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="運用ルール_必読" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="グループ一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="配信スケジュール" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="全町リスト_五十音順" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
